--- a/diseases/d165/2000-2004.xlsx
+++ b/diseases/d165/2000-2004.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1710,6 +1715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2251,6 +2261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2792,6 +2807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3333,6 +3353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3874,6 +3899,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4415,6 +4445,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4956,6 +4991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5497,6 +5537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6038,6 +6083,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6579,6 +6629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7120,6 +7175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7661,6 +7721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8202,6 +8267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8743,6 +8813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9284,6 +9359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9825,6 +9905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10366,6 +10451,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10907,6 +10997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11448,6 +11543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11989,6 +12089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12530,6 +12635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13071,6 +13181,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13612,6 +13727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14153,6 +14273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14694,6 +14819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15235,6 +15365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15776,6 +15911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16317,6 +16457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16858,6 +17003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17399,6 +17549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17940,6 +18095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18481,6 +18641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19022,6 +19187,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19563,6 +19733,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20104,6 +20279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20645,6 +20825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20793,6 +20978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21334,6 +21524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21482,6 +21677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22023,6 +22223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22171,6 +22376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22712,6 +22922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22860,6 +23075,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23401,6 +23621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23549,6 +23774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24090,6 +24320,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24238,6 +24473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24779,6 +25019,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24927,6 +25172,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25468,6 +25718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25616,6 +25871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26157,6 +26417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26305,6 +26570,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26846,6 +27116,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26994,6 +27269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27535,6 +27815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27683,6 +27968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28224,6 +28514,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28372,6 +28667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28913,6 +29213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29061,6 +29366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29602,6 +29912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29750,6 +30065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30291,6 +30611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30439,6 +30764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30980,6 +31310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31128,6 +31463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31669,6 +32009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31817,6 +32162,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32358,6 +32708,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32506,6 +32861,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33047,6 +33407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33195,6 +33560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33736,6 +34106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33884,6 +34259,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34425,6 +34805,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34573,6 +34958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35114,6 +35504,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35262,6 +35657,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35803,6 +36203,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35951,6 +36356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36492,6 +36902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36638,6 +37053,11 @@
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">

--- a/diseases/d165/2000-2004.xlsx
+++ b/diseases/d165/2000-2004.xlsx
@@ -1164,6 +1164,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1176,13 +1181,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -1695,6 +1710,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1707,13 +1727,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2226,6 +2256,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2238,13 +2273,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -2757,6 +2802,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2769,13 +2819,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3288,6 +3348,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3300,13 +3365,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -3819,6 +3894,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3831,13 +3911,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4350,6 +4440,11 @@
       <c r="R22" t="n">
         <v>0.01491499052003203</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4362,13 +4457,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -4881,6 +4986,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4893,13 +5003,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5412,6 +5532,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5424,13 +5549,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -5943,6 +6078,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5955,13 +6095,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -6474,6 +6624,11 @@
       <c r="R34" t="n">
         <v>0.02982998104006405</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6486,13 +6641,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7005,6 +7170,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7017,13 +7187,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -7536,6 +7716,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7548,13 +7733,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8067,6 +8262,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8079,13 +8279,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8598,6 +8808,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8610,13 +8825,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9129,6 +9354,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9141,13 +9371,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -9660,6 +9900,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9672,13 +9917,23 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10191,6 +10446,11 @@
       <c r="R55" t="n">
         <v>0.0295236136135449</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10203,13 +10463,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -10722,6 +10992,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10734,13 +11009,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11253,6 +11538,11 @@
       <c r="R61" t="n">
         <v>0.0295236136135449</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11265,13 +11555,23 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -11784,6 +12084,11 @@
       <c r="R64" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11796,13 +12101,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12315,6 +12630,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12327,13 +12647,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -12846,6 +13176,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12858,13 +13193,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -13377,6 +13722,11 @@
       <c r="R73" t="n">
         <v>0.01476180680677245</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13389,13 +13739,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -13908,6 +14268,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13920,13 +14285,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14439,6 +14814,11 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14451,13 +14831,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -14970,6 +15360,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14982,13 +15377,23 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -15501,6 +15906,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15513,13 +15923,23 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -16032,6 +16452,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16044,13 +16469,23 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -17190,6 +17625,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17202,13 +17642,23 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
       </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV94" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -18348,6 +18798,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18360,13 +18815,23 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -19506,6 +19971,11 @@
       <c r="R106" t="n">
         <v>0.01465972899878376</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19518,13 +19988,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -21291,6 +21771,11 @@
       <c r="R115" t="n">
         <v>0.02931945799756751</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21303,13 +21788,23 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV115" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23076,6 +23571,11 @@
       <c r="R124" t="n">
         <v>0.01465972899878376</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23088,13 +23588,23 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
       </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV124" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25488,6 +25998,11 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25500,13 +26015,23 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
       </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV136" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26646,6 +27171,11 @@
       <c r="R142" t="n">
         <v>0.01465972899878376</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26658,13 +27188,23 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27804,6 +28344,11 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27816,13 +28361,23 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
       </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV148" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29100,6 +29655,11 @@
       <c r="R155" t="n">
         <v>0.04373875048449779</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29112,13 +29672,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30396,6 +30966,11 @@
       <c r="R162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30408,13 +30983,23 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
       </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV162" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31692,6 +32277,11 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31704,13 +32294,23 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
       </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV169" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32988,6 +33588,11 @@
       <c r="R176" t="n">
         <v>0</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33000,13 +33605,23 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
       </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV176" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34284,6 +34899,11 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34296,13 +34916,23 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
       </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV183" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36207,6 +36837,11 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36219,13 +36854,23 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
       </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV193" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39774,6 +40419,11 @@
       <c r="R211" t="n">
         <v>0.01457958349483259</v>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39786,13 +40436,23 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
       </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV211" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43104,6 +43764,11 @@
       <c r="R228" t="n">
         <v>0</v>
       </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43116,13 +43781,23 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
         <v>0</v>
       </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV228" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46671,6 +47346,11 @@
       <c r="R246" t="n">
         <v>0.01457958349483259</v>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46683,13 +47363,23 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
       </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV246" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48984,6 +49674,11 @@
       <c r="R258" t="n">
         <v>0.02915916698966519</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48996,13 +49691,23 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
       </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV258" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50280,6 +50985,11 @@
       <c r="R265" t="n">
         <v>0.1312162514534934</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50292,13 +51002,23 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
       </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV265" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51576,6 +52296,11 @@
       <c r="R272" t="n">
         <v>0.08710594630920128</v>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51588,13 +52313,23 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
         <v>0</v>
       </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV272" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53499,6 +54234,11 @@
       <c r="R282" t="n">
         <v>0.08710594630920128</v>
       </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53511,13 +54251,23 @@
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS282" t="inlineStr"/>
       <c r="AT282" t="n">
         <v>0</v>
       </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV282" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -57693,6 +58443,11 @@
       <c r="R303" t="n">
         <v>0.07258828859100107</v>
       </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA303" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57705,13 +58460,23 @@
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR303" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr"/>
       <c r="AT303" t="n">
         <v>0</v>
       </c>
+      <c r="AU303" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV303" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -60006,6 +60771,11 @@
       <c r="R315" t="n">
         <v>0.01451765771820021</v>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA315" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60018,13 +60788,23 @@
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS315" t="inlineStr"/>
       <c r="AT315" t="n">
         <v>0</v>
       </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV315" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -60675,6 +61455,11 @@
       <c r="R319" t="n">
         <v>0.01451765771820021</v>
       </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60687,13 +61472,23 @@
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS319" t="inlineStr"/>
       <c r="AT319" t="n">
         <v>0</v>
       </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV319" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -63225,6 +64020,11 @@
       <c r="R332" t="n">
         <v>0.02903531543640043</v>
       </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63237,13 +64037,23 @@
       </c>
       <c r="AP332" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR332" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS332" t="inlineStr"/>
       <c r="AT332" t="n">
         <v>0</v>
       </c>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV332" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -65148,6 +65958,11 @@
       <c r="R342" t="n">
         <v>0</v>
       </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA342" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -65160,13 +65975,23 @@
       </c>
       <c r="AP342" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR342" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS342" t="inlineStr"/>
       <c r="AT342" t="n">
         <v>0</v>
       </c>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV342" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -68088,6 +68913,11 @@
       <c r="R357" t="n">
         <v>0</v>
       </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA357" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -68100,13 +68930,23 @@
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS357" t="inlineStr"/>
       <c r="AT357" t="n">
         <v>0</v>
       </c>
+      <c r="AU357" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV357" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -69384,6 +70224,11 @@
       <c r="R364" t="n">
         <v>0</v>
       </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA364" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -69396,13 +70241,23 @@
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS364" t="inlineStr"/>
       <c r="AT364" t="n">
         <v>0</v>
       </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV364" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -72951,6 +73806,11 @@
       <c r="R382" t="n">
         <v>0</v>
       </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA382" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -72963,13 +73823,23 @@
       </c>
       <c r="AP382" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS382" t="inlineStr"/>
       <c r="AT382" t="n">
         <v>0</v>
       </c>
+      <c r="AU382" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV382" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -75501,6 +76371,11 @@
       <c r="R395" t="n">
         <v>0</v>
       </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -75513,13 +76388,23 @@
       </c>
       <c r="AP395" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR395" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS395" t="inlineStr"/>
       <c r="AT395" t="n">
         <v>0</v>
       </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV395" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -77424,6 +78309,11 @@
       <c r="R405" t="n">
         <v>0.02903531543640043</v>
       </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA405" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -77436,12 +78326,22 @@
       </c>
       <c r="AP405" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR405" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS405" t="inlineStr"/>
       <c r="AT405" t="n">
         <v>0</v>
+      </c>
+      <c r="AU405" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV405" t="inlineStr">
         <is>
